--- a/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-pr-biobank-zellinie-organoid.xlsx
+++ b/branches/chore/update-miabis-1.3.0/StructureDefinition-mii-pr-biobank-zellinie-organoid.xlsx
@@ -1017,7 +1017,7 @@
     <t>miabis-type</t>
   </si>
   <si>
-    <t>https://fhir.bbmri-eric.eu/ValueSet/miabis-material-type-vs</t>
+    <t>https://fhir.bbmri-eric.eu/ValueSet/miabis-detailed-sample-type-vs</t>
   </si>
   <si>
     <t>Specimen.type.coding:miabis-type.id</t>
